--- a/backend/excel-templates/test-data/bachelor_student_users_test_data.xlsx
+++ b/backend/excel-templates/test-data/bachelor_student_users_test_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Students" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G31"/>
+  <cols>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,22 +433,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ram.sharma@pcampus.edu.np</v>
+        <v>student1@pcampus.edu.np</v>
       </c>
       <c r="B2" t="str">
-        <v>pass123</v>
+        <v>subesh</v>
       </c>
       <c r="C2" t="str">
-        <v>Ram</v>
+        <v>Student</v>
       </c>
       <c r="D2" t="str">
-        <v>Sharma</v>
+        <v>1</v>
       </c>
       <c r="E2" t="str">
-        <v>078BCT001</v>
+        <v>78BEI001</v>
       </c>
       <c r="F2" t="str">
-        <v>BCT</v>
+        <v>BEI</v>
       </c>
       <c r="G2" t="str">
         <v>BACHELOR</v>
@@ -447,22 +456,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>sita.poudel@pcampus.edu.np</v>
+        <v>student2@pcampus.edu.np</v>
       </c>
       <c r="B3" t="str">
-        <v>pass123</v>
+        <v>subesh</v>
       </c>
       <c r="C3" t="str">
-        <v>Sita</v>
+        <v>Student</v>
       </c>
       <c r="D3" t="str">
-        <v>Poudel</v>
+        <v>2</v>
       </c>
       <c r="E3" t="str">
-        <v>078BEI002</v>
+        <v>78BCT002</v>
       </c>
       <c r="F3" t="str">
-        <v>BEI</v>
+        <v>BCT</v>
       </c>
       <c r="G3" t="str">
         <v>BACHELOR</v>
@@ -470,30 +479,651 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>krishna.thapa@pcampus.edu.np</v>
+        <v>student3@pcampus.edu.np</v>
       </c>
       <c r="B4" t="str">
-        <v>pass123</v>
+        <v>subesh</v>
       </c>
       <c r="C4" t="str">
-        <v>Krishna</v>
+        <v>Student</v>
       </c>
       <c r="D4" t="str">
-        <v>Thapa</v>
+        <v>3</v>
       </c>
       <c r="E4" t="str">
-        <v>078BCT003</v>
+        <v>78BEI003</v>
       </c>
       <c r="F4" t="str">
-        <v>BCT</v>
+        <v>BEI</v>
       </c>
       <c r="G4" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>student4@pcampus.edu.np</v>
+      </c>
+      <c r="B5" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D5" t="str">
+        <v>4</v>
+      </c>
+      <c r="E5" t="str">
+        <v>78BCT004</v>
+      </c>
+      <c r="F5" t="str">
+        <v>BCT</v>
+      </c>
+      <c r="G5" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>student5@pcampus.edu.np</v>
+      </c>
+      <c r="B6" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D6" t="str">
+        <v>5</v>
+      </c>
+      <c r="E6" t="str">
+        <v>78BEI005</v>
+      </c>
+      <c r="F6" t="str">
+        <v>BEI</v>
+      </c>
+      <c r="G6" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>student6@pcampus.edu.np</v>
+      </c>
+      <c r="B7" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D7" t="str">
+        <v>6</v>
+      </c>
+      <c r="E7" t="str">
+        <v>78BCT006</v>
+      </c>
+      <c r="F7" t="str">
+        <v>BCT</v>
+      </c>
+      <c r="G7" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>student7@pcampus.edu.np</v>
+      </c>
+      <c r="B8" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D8" t="str">
+        <v>7</v>
+      </c>
+      <c r="E8" t="str">
+        <v>78BEI007</v>
+      </c>
+      <c r="F8" t="str">
+        <v>BEI</v>
+      </c>
+      <c r="G8" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>student8@pcampus.edu.np</v>
+      </c>
+      <c r="B9" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D9" t="str">
+        <v>8</v>
+      </c>
+      <c r="E9" t="str">
+        <v>78BCT008</v>
+      </c>
+      <c r="F9" t="str">
+        <v>BCT</v>
+      </c>
+      <c r="G9" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>student9@pcampus.edu.np</v>
+      </c>
+      <c r="B10" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D10" t="str">
+        <v>9</v>
+      </c>
+      <c r="E10" t="str">
+        <v>78BEI009</v>
+      </c>
+      <c r="F10" t="str">
+        <v>BEI</v>
+      </c>
+      <c r="G10" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>student10@pcampus.edu.np</v>
+      </c>
+      <c r="B11" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D11" t="str">
+        <v>10</v>
+      </c>
+      <c r="E11" t="str">
+        <v>78BCT010</v>
+      </c>
+      <c r="F11" t="str">
+        <v>BCT</v>
+      </c>
+      <c r="G11" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>student11@pcampus.edu.np</v>
+      </c>
+      <c r="B12" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D12" t="str">
+        <v>11</v>
+      </c>
+      <c r="E12" t="str">
+        <v>78BEI011</v>
+      </c>
+      <c r="F12" t="str">
+        <v>BEI</v>
+      </c>
+      <c r="G12" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>student12@pcampus.edu.np</v>
+      </c>
+      <c r="B13" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D13" t="str">
+        <v>12</v>
+      </c>
+      <c r="E13" t="str">
+        <v>79BCT012</v>
+      </c>
+      <c r="F13" t="str">
+        <v>BCT</v>
+      </c>
+      <c r="G13" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>student13@pcampus.edu.np</v>
+      </c>
+      <c r="B14" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D14" t="str">
+        <v>13</v>
+      </c>
+      <c r="E14" t="str">
+        <v>79BEI013</v>
+      </c>
+      <c r="F14" t="str">
+        <v>BEI</v>
+      </c>
+      <c r="G14" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>student14@pcampus.edu.np</v>
+      </c>
+      <c r="B15" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D15" t="str">
+        <v>14</v>
+      </c>
+      <c r="E15" t="str">
+        <v>79BCT014</v>
+      </c>
+      <c r="F15" t="str">
+        <v>BCT</v>
+      </c>
+      <c r="G15" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>student15@pcampus.edu.np</v>
+      </c>
+      <c r="B16" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D16" t="str">
+        <v>15</v>
+      </c>
+      <c r="E16" t="str">
+        <v>79BEI015</v>
+      </c>
+      <c r="F16" t="str">
+        <v>BEI</v>
+      </c>
+      <c r="G16" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>student16@pcampus.edu.np</v>
+      </c>
+      <c r="B17" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D17" t="str">
+        <v>16</v>
+      </c>
+      <c r="E17" t="str">
+        <v>79BCT016</v>
+      </c>
+      <c r="F17" t="str">
+        <v>BCT</v>
+      </c>
+      <c r="G17" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>student17@pcampus.edu.np</v>
+      </c>
+      <c r="B18" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D18" t="str">
+        <v>17</v>
+      </c>
+      <c r="E18" t="str">
+        <v>79BEI017</v>
+      </c>
+      <c r="F18" t="str">
+        <v>BEI</v>
+      </c>
+      <c r="G18" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>student18@pcampus.edu.np</v>
+      </c>
+      <c r="B19" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D19" t="str">
+        <v>18</v>
+      </c>
+      <c r="E19" t="str">
+        <v>79BCT018</v>
+      </c>
+      <c r="F19" t="str">
+        <v>BCT</v>
+      </c>
+      <c r="G19" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>student19@pcampus.edu.np</v>
+      </c>
+      <c r="B20" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D20" t="str">
+        <v>19</v>
+      </c>
+      <c r="E20" t="str">
+        <v>79BEI019</v>
+      </c>
+      <c r="F20" t="str">
+        <v>BEI</v>
+      </c>
+      <c r="G20" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>student20@pcampus.edu.np</v>
+      </c>
+      <c r="B21" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D21" t="str">
+        <v>20</v>
+      </c>
+      <c r="E21" t="str">
+        <v>79BCT020</v>
+      </c>
+      <c r="F21" t="str">
+        <v>BCT</v>
+      </c>
+      <c r="G21" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>student21@pcampus.edu.np</v>
+      </c>
+      <c r="B22" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D22" t="str">
+        <v>21</v>
+      </c>
+      <c r="E22" t="str">
+        <v>79BEI021</v>
+      </c>
+      <c r="F22" t="str">
+        <v>BEI</v>
+      </c>
+      <c r="G22" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>student22@pcampus.edu.np</v>
+      </c>
+      <c r="B23" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D23" t="str">
+        <v>22</v>
+      </c>
+      <c r="E23" t="str">
+        <v>79BCT022</v>
+      </c>
+      <c r="F23" t="str">
+        <v>BCT</v>
+      </c>
+      <c r="G23" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>student23@pcampus.edu.np</v>
+      </c>
+      <c r="B24" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D24" t="str">
+        <v>23</v>
+      </c>
+      <c r="E24" t="str">
+        <v>79BEI023</v>
+      </c>
+      <c r="F24" t="str">
+        <v>BEI</v>
+      </c>
+      <c r="G24" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>student24@pcampus.edu.np</v>
+      </c>
+      <c r="B25" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D25" t="str">
+        <v>24</v>
+      </c>
+      <c r="E25" t="str">
+        <v>80BCT024</v>
+      </c>
+      <c r="F25" t="str">
+        <v>BCT</v>
+      </c>
+      <c r="G25" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>student25@pcampus.edu.np</v>
+      </c>
+      <c r="B26" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D26" t="str">
+        <v>25</v>
+      </c>
+      <c r="E26" t="str">
+        <v>80BEI025</v>
+      </c>
+      <c r="F26" t="str">
+        <v>BEI</v>
+      </c>
+      <c r="G26" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>student26@pcampus.edu.np</v>
+      </c>
+      <c r="B27" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D27" t="str">
+        <v>26</v>
+      </c>
+      <c r="E27" t="str">
+        <v>80BCT026</v>
+      </c>
+      <c r="F27" t="str">
+        <v>BCT</v>
+      </c>
+      <c r="G27" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>student27@pcampus.edu.np</v>
+      </c>
+      <c r="B28" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D28" t="str">
+        <v>27</v>
+      </c>
+      <c r="E28" t="str">
+        <v>80BEI027</v>
+      </c>
+      <c r="F28" t="str">
+        <v>BEI</v>
+      </c>
+      <c r="G28" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>student28@pcampus.edu.np</v>
+      </c>
+      <c r="B29" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D29" t="str">
+        <v>28</v>
+      </c>
+      <c r="E29" t="str">
+        <v>80BCT028</v>
+      </c>
+      <c r="F29" t="str">
+        <v>BCT</v>
+      </c>
+      <c r="G29" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>student29@pcampus.edu.np</v>
+      </c>
+      <c r="B30" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D30" t="str">
+        <v>29</v>
+      </c>
+      <c r="E30" t="str">
+        <v>80BEI029</v>
+      </c>
+      <c r="F30" t="str">
+        <v>BEI</v>
+      </c>
+      <c r="G30" t="str">
+        <v>BACHELOR</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>student30@pcampus.edu.np</v>
+      </c>
+      <c r="B31" t="str">
+        <v>subesh</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Student</v>
+      </c>
+      <c r="D31" t="str">
+        <v>30</v>
+      </c>
+      <c r="E31" t="str">
+        <v>80BCT030</v>
+      </c>
+      <c r="F31" t="str">
+        <v>BCT</v>
+      </c>
+      <c r="G31" t="str">
         <v>BACHELOR</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G31"/>
   </ignoredErrors>
 </worksheet>
 </file>